--- a/evaluation/corpus/phoenix_evaluation.xlsx
+++ b/evaluation/corpus/phoenix_evaluation.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,233 +413,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Embedding Dimension</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vector Database</t>
+          <t>Engine A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Qdrant</t>
-        </is>
+      <c r="B2" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C2" t="n">
+        <v>768</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>qwen3:4b-instruct</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Embedding Model</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nomic-embed-text</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Embedding Dimension</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Dense + Lexical Fusion</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>RRF</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Order ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Engine A</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>Engine B</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10400</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Engine A</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E4" t="n">
-        <v>14400</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Engine C</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Engine B</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9100</v>
+      <c r="B3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>768</v>
       </c>
     </row>
   </sheetData>
